--- a/flipkart-automation-project/testdata/TestData.xlsx
+++ b/flipkart-automation-project/testdata/TestData.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thatomoetanalo\Documents\flipkart-automation\flipkart-automation-project\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7C16C0B-EE50-431E-8100-CC2B72F25139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AD3228-5109-4FC9-9BD5-75BD8E5DDE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D9930F9D-EA75-4CE4-BCA2-1D8B781B7D35}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{D9930F9D-EA75-4CE4-BCA2-1D8B781B7D35}"/>
   </bookViews>
   <sheets>
     <sheet name="HomePage" sheetId="1" r:id="rId1"/>
-    <sheet name="SearchPage" sheetId="4" r:id="rId2"/>
-    <sheet name="ProductPage" sheetId="5" r:id="rId3"/>
+    <sheet name="Navigation" sheetId="6" r:id="rId2"/>
+    <sheet name="SearchPage" sheetId="4" r:id="rId3"/>
+    <sheet name="ProductPage" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
   <si>
     <t>Test Case Name</t>
   </si>
@@ -182,6 +183,69 @@
   </si>
   <si>
     <t>Category Links Visible</t>
+  </si>
+  <si>
+    <t>TC014</t>
+  </si>
+  <si>
+    <t>Electronics Page Loads</t>
+  </si>
+  <si>
+    <t>Title contains Electronics</t>
+  </si>
+  <si>
+    <t>TC015</t>
+  </si>
+  <si>
+    <t>Search Bar Visible</t>
+  </si>
+  <si>
+    <t>Search bar displayed</t>
+  </si>
+  <si>
+    <t>TC016</t>
+  </si>
+  <si>
+    <t>Page URL Correct</t>
+  </si>
+  <si>
+    <t>URL contains flipkart.com</t>
+  </si>
+  <si>
+    <t>TC017</t>
+  </si>
+  <si>
+    <t>Search Updates Title</t>
+  </si>
+  <si>
+    <t>Title updates after search</t>
+  </si>
+  <si>
+    <t>TC018</t>
+  </si>
+  <si>
+    <t>Grocery Page Loads</t>
+  </si>
+  <si>
+    <t>URL contains grocery</t>
+  </si>
+  <si>
+    <t>TC019</t>
+  </si>
+  <si>
+    <t>Homepage URL Correct</t>
+  </si>
+  <si>
+    <t>URL equals flipkart.com</t>
+  </si>
+  <si>
+    <t>TC020</t>
+  </si>
+  <si>
+    <t>Search Bar Placeholder Visible</t>
+  </si>
+  <si>
+    <t>Search bar visible</t>
   </si>
 </sst>
 </file>
@@ -640,6 +704,134 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E1FD627-8813-4B01-B3F0-58330B9E431E}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" customWidth="1"/>
+    <col min="4" max="4" width="47.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F195F548-718C-4264-AF73-25144C547C2A}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -754,7 +946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{148EE940-46A8-4C6E-83B6-61456682A3D3}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
